--- a/data/analysis_ministral_3_14b_qwen2_audio/multimodal_event_eval_ministral_3_14b_qwen2_audio_w1_0s_h0_5s.xlsx
+++ b/data/analysis_ministral_3_14b_qwen2_audio/multimodal_event_eval_ministral_3_14b_qwen2_audio_w1_0s_h0_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -112,19 +112,19 @@
     <t>sound: shout(0-156), sound: shout(204-240), sound: gunshot_or_explosion(48-72), sound: impact(108-216), visual: carrying(120-120), visual: physical_altercation(72-72)</t>
   </si>
   <si>
-    <t>sound: impact(0-36), sound: impact(60-96), sound: impact(120-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: gunshot_visible(168-168), visual: running(120-240), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-120), visual: vehicle_collision(216-240)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-48), sound: shout(72-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(48-72), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-144), visual: suspicious_near_vehicle(0-0)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-24), sound: shout(48-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
+    <t>sound: impact(0-216), sound: shout(24-72), sound: shout(216-240), sound: gunshot_or_explosion(84-132), sound: gunshot_or_explosion(168-228), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: gunshot_visible(168-168), visual: running(120-240), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-120), visual: vehicle_collision(216-240)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-60), sound: impact(192-240), sound: shout(24-192), sound: gunshot_or_explosion(48-84), sound: horn(180-204), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(48-72), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-144), visual: suspicious_near_vehicle(0-0)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-240), sound: impact(12-60), sound: gunshot_or_explosion(108-144), sound: gunshot_or_explosion(192-216), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-36), sound: impact(24-60), sound: impact(120-144), sound: impact(180-204), sound: engine(48-96), sound: engine(168-228), sound: shout(84-240), visual: explosion_visible(24-240), visual: running(24-240), visual: running(120-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: impact(12-108), sound: impact(132-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: enter_or_exit_vehicle(0-0), visual: explosion_visible(72-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: explosion_visible(72-72), visual: explosion_visible(216-240), visual: explosion_visible(48-216), visual: explosion_visible(168-168), visual: running(96-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(216-240), visual: vehicle_collision(48-240), visual: vehicle_collision(48-48), visual: vehicle_collision(192-240), visual: vehicle_collision(72-120), visual: vehicle_collision(216-240)</t>
+    <t>sound: engine(0-24), sound: impact(12-156), sound: gunshot_or_explosion(24-48), sound: gunshot_or_explosion(120-144), sound: shout(96-240), visual: enter_or_exit_vehicle(0-0), visual: explosion_visible(72-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: explosion_visible(72-72), visual: explosion_visible(216-240), visual: explosion_visible(48-216), visual: explosion_visible(168-168), visual: running(96-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(216-240), visual: vehicle_collision(48-240), visual: vehicle_collision(48-48), visual: vehicle_collision(192-240), visual: vehicle_collision(72-120), visual: vehicle_collision(216-240)</t>
   </si>
   <si>
     <t>NO</t>
@@ -139,16 +139,16 @@
     <t>sound: shout(0-84), sound: impact(72-96), sound: impact(216-240), sound: engine(84-228), sound: tire_squeal(180-216), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
-    <t>sound: shout(0-72), sound: shout(96-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-96), sound: engine(120-204), visual: 9(168-168), visual: suspicious_near_vehicle(0-48)</t>
-  </si>
-  <si>
-    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-180), sound: shout(204-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(192-192)</t>
+    <t>sound: shout(0-132), sound: shout(192-216), sound: impact(36-108), sound: impact(144-168), sound: impact(204-240), sound: engine(72-204), visual: 9(168-168), visual: suspicious_near_vehicle(0-48)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-48), sound: shout(36-84), sound: shout(156-240), sound: impact(72-216), sound: engine(84-120), sound: gunshot_or_explosion(120-144), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(192-192)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: impact(12-108), sound: impact(204-240), sound: tire_squeal(24-48), sound: shout(36-60), sound: shout(120-216), sound: gunshot_or_explosion(96-132), visual: 9(240-240), visual: enter_or_exit_vehicle(168-168), visual: enter_or_exit_vehicle(240-240), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(72-168), visual: suspicious_near_vehicle(72-144), visual: suspicious_near_vehicle(192-240), visual: vehicle_collision(72-240), visual: vehicle_collision(96-240), visual: vehicle_collision(72-72)</t>
   </si>
   <si>
-    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-84), sound: shout(108-168), sound: impact(72-240), visual: 9(120-120), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(216-240), visual: enter_or_exit_vehicle(168-192), visual: enter_or_exit_vehicle(168-240), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-144), visual: vehicle_collision(216-240), visual: vehicle_collision(168-192)</t>
+    <t>sound: engine(0-24), sound: horn(12-60), sound: shout(48-168), sound: impact(72-240), visual: 9(120-120), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(216-240), visual: enter_or_exit_vehicle(168-192), visual: enter_or_exit_vehicle(168-240), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-144), visual: vehicle_collision(216-240), visual: vehicle_collision(168-192)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(24-48), visual: suspicious_near_vehicle(24-216), visual: suspicious_near_vehicle(240-240)</t>
@@ -169,13 +169,13 @@
     <t>visual: carrying(48-72), visual: carrying(192-192), visual: carrying(0-24), visual: carrying(96-96), visual: carrying(96-96), visual: carrying(48-72), visual: carrying(144-192), visual: carrying(120-120), visual: carrying(24-24), visual: carrying(144-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(96-168), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-168)</t>
   </si>
   <si>
-    <t>sound: shout(0-228), sound: impact(132-156), sound: impact(180-240), visual: physical_altercation(48-120)</t>
-  </si>
-  <si>
-    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-180), sound: impact(204-240), visual: physical_altercation(48-120), visual: running(24-120), visual: running(24-120), visual: running(192-192), visual: running(192-192)</t>
-  </si>
-  <si>
-    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-192), sound: shout(216-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: carrying(0-0), visual: carrying(24-48), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-72)</t>
+    <t>sound: shout(0-228), sound: impact(132-240), visual: physical_altercation(48-120)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-216), sound: gunshot_or_explosion(120-144), sound: impact(156-240), visual: physical_altercation(48-120), visual: running(24-120), visual: running(24-120), visual: running(192-192), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: impact(0-144), sound: impact(180-228), sound: shout(12-48), sound: shout(144-240), sound: gunshot_or_explosion(108-132), sound: tire_squeal(132-156), visual: carrying(0-0), visual: carrying(24-48), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-72)</t>
   </si>
   <si>
     <t>sound: impact(0-24), sound: impact(72-144), sound: impact(192-240), sound: shout(12-192), sound: engine(180-204), visual: enter_or_exit_vehicle(48-240), visual: running(0-0), visual: suspicious_near_vehicle(0-192)</t>
@@ -187,7 +187,7 @@
     <t>sound: engine(0-24), sound: horn(12-72), sound: impact(60-240), sound: gunshot_or_explosion(84-120), sound: shout(120-144), visual: enter_or_exit_vehicle(168-240), visual: enter_or_exit_vehicle(192-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(192-216), visual: vehicle_collision(72-240), visual: vehicle_collision(72-240)</t>
   </si>
   <si>
-    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-132), sound: shout(156-216), sound: gunshot_or_explosion(36-60), sound: impact(48-96), sound: impact(120-240), visual: enter_or_exit_vehicle(168-168), visual: enter_or_exit_vehicle(240-240), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(48-240), visual: vehicle_collision(96-240), visual: vehicle_collision(48-72)</t>
+    <t>sound: tire_squeal(0-24), sound: shout(12-48), sound: shout(84-216), sound: gunshot_or_explosion(36-60), sound: impact(48-240), visual: enter_or_exit_vehicle(168-168), visual: enter_or_exit_vehicle(240-240), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(48-240), visual: vehicle_collision(96-240), visual: vehicle_collision(48-72)</t>
   </si>
   <si>
     <t>visual: carrying(0-0), visual: enter_or_exit_vehicle(72-168), visual: running(216-216), visual: suspicious_near_vehicle(0-216)</t>
@@ -591,19 +591,19 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.571</v>
+        <v>0.8</v>
       </c>
       <c r="C2">
         <v>0.8</v>
       </c>
       <c r="D2">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1694,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1736,7 +1736,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1745,23 +1745,6 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2087,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2129,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2138,23 +2121,6 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
         <v>22</v>
       </c>
     </row>
